--- a/ML/ig/StructureDefinition-OffreOperationnelle.xlsx
+++ b/ML/ig/StructureDefinition-OffreOperationnelle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-02T15:33:27+00:00</t>
+    <t>2025-12-09T08:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML/ig/StructureDefinition-OffreOperationnelle.xlsx
+++ b/ML/ig/StructureDefinition-OffreOperationnelle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T08:48:05+00:00</t>
+    <t>2026-01-08T08:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML/ig/StructureDefinition-OffreOperationnelle.xlsx
+++ b/ML/ig/StructureDefinition-OffreOperationnelle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-08T08:09:01+00:00</t>
+    <t>2026-01-08T08:10:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML/ig/StructureDefinition-OffreOperationnelle.xlsx
+++ b/ML/ig/StructureDefinition-OffreOperationnelle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-08T08:10:58+00:00</t>
+    <t>2026-01-08T08:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML/ig/StructureDefinition-OffreOperationnelle.xlsx
+++ b/ML/ig/StructureDefinition-OffreOperationnelle.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-08T08:28:29+00:00</t>
+    <t>2026-01-08T09:04:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
